--- a/workbench/templates_builtin/监理模板_设备重量确认单.xlsx
+++ b/workbench/templates_builtin/监理模板_设备重量确认单.xlsx
@@ -1324,7 +1324,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="5.20833333333333" customWidth="1" style="2" min="1" max="1"/>
@@ -1797,327 +1797,35 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="33" customHeight="1" s="14">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>{{车间}}设备重量确认单2</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="25" customHeight="1" s="14">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>序号</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>设备名称</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>型号规格及技术性能</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>单位</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>数量</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>设备重量(t)</t>
-        </is>
-      </c>
-      <c r="G19" s="15" t="n"/>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>重量依据</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="25" customHeight="1" s="14">
-      <c r="A20" s="16" t="n"/>
-      <c r="B20" s="16" t="n"/>
-      <c r="C20" s="16" t="n"/>
-      <c r="D20" s="16" t="n"/>
-      <c r="E20" s="16" t="n"/>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>单重</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>总重</t>
-        </is>
-      </c>
-      <c r="H20" s="16" t="n"/>
-    </row>
-    <row r="21" ht="25" customFormat="1" customHeight="1" s="1">
-      <c r="A21" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>电液动双缸驱动平板闸门</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>DPZ-S100，1000×1000</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 台</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H21" s="11" t="inlineStr">
-        <is>
-          <t>厂家随机清单</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="25" customFormat="1" customHeight="1" s="1">
-      <c r="A22" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>微雾抑尘系统</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>HPF-42D</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 台</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" s="8" t="n"/>
-      <c r="G22" s="8" t="n"/>
-      <c r="H22" s="11" t="inlineStr">
-        <is>
-          <t>厂家随机清单</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="25" customFormat="1" customHeight="1" s="1">
-      <c r="A23" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="B23" s="8" t="n"/>
-      <c r="C23" s="8" t="n"/>
-      <c r="D23" s="8" t="n"/>
-      <c r="E23" s="8" t="n"/>
-      <c r="F23" s="8" t="n"/>
-      <c r="G23" s="8" t="n"/>
-      <c r="H23" s="11" t="n"/>
-    </row>
-    <row r="24" ht="25" customFormat="1" customHeight="1" s="1">
-      <c r="A24" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="B24" s="8" t="n"/>
-      <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="n"/>
-      <c r="E24" s="8" t="n"/>
-      <c r="F24" s="8" t="n"/>
-      <c r="G24" s="8" t="n"/>
-      <c r="H24" s="11" t="n"/>
-    </row>
-    <row r="25" ht="25" customFormat="1" customHeight="1" s="1">
-      <c r="A25" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="B25" s="8" t="n"/>
-      <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="n"/>
-      <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="n"/>
-      <c r="G25" s="8" t="n"/>
-      <c r="H25" s="11" t="n"/>
-    </row>
-    <row r="26" ht="25" customFormat="1" customHeight="1" s="1">
-      <c r="A26" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="B26" s="8" t="n"/>
-      <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="n"/>
-      <c r="E26" s="8" t="n"/>
-      <c r="F26" s="8" t="n"/>
-      <c r="G26" s="8" t="n"/>
-      <c r="H26" s="11" t="n"/>
-    </row>
-    <row r="27" ht="25" customFormat="1" customHeight="1" s="1">
-      <c r="A27" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B27" s="8" t="n"/>
-      <c r="C27" s="8" t="n"/>
-      <c r="D27" s="8" t="n"/>
-      <c r="E27" s="8" t="n"/>
-      <c r="F27" s="8" t="n"/>
-      <c r="G27" s="8" t="n"/>
-      <c r="H27" s="11" t="n"/>
-    </row>
-    <row r="28" ht="25" customFormat="1" customHeight="1" s="1">
-      <c r="A28" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="B28" s="8" t="n"/>
-      <c r="C28" s="8" t="n"/>
-      <c r="D28" s="8" t="n"/>
-      <c r="E28" s="8" t="n"/>
-      <c r="F28" s="8" t="n"/>
-      <c r="G28" s="8" t="n"/>
-      <c r="H28" s="11" t="n"/>
-    </row>
-    <row r="29" ht="25" customFormat="1" customHeight="1" s="1">
-      <c r="A29" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="B29" s="8" t="n"/>
-      <c r="C29" s="8" t="n"/>
-      <c r="D29" s="8" t="n"/>
-      <c r="E29" s="8" t="n"/>
-      <c r="F29" s="8" t="n"/>
-      <c r="G29" s="8" t="n"/>
-      <c r="H29" s="11" t="n"/>
-    </row>
-    <row r="30" ht="25" customFormat="1" customHeight="1" s="1">
-      <c r="A30" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="B30" s="8" t="n"/>
-      <c r="C30" s="8" t="n"/>
-      <c r="D30" s="8" t="n"/>
-      <c r="E30" s="8" t="n"/>
-      <c r="F30" s="8" t="n"/>
-      <c r="G30" s="8" t="n"/>
-      <c r="H30" s="11" t="n"/>
-    </row>
-    <row r="31" ht="25" customFormat="1" customHeight="1" s="1">
-      <c r="A31" s="12" t="inlineStr">
-        <is>
-          <t>备注：KKCC由物流园将设备转运并卸车至{{车间}}</t>
-        </is>
-      </c>
-      <c r="B31" s="18" t="n"/>
-      <c r="C31" s="18" t="n"/>
-      <c r="D31" s="18" t="n"/>
-      <c r="E31" s="18" t="n"/>
-      <c r="F31" s="18" t="n"/>
-      <c r="G31" s="18" t="n"/>
-      <c r="H31" s="15" t="n"/>
-    </row>
-    <row r="32" ht="34" customFormat="1" customHeight="1" s="1">
-      <c r="A32" s="13" t="inlineStr">
-        <is>
-          <t>监理单位：{{监理单位}}</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>建设单位：{{建设单位}}</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="n"/>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>施工单位：{{施工单位}}</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="n"/>
-      <c r="G32" s="2" t="n"/>
-    </row>
-    <row r="33" ht="34" customFormat="1" customHeight="1" s="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>现场监理：</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>现场负责人：</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="n"/>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>编制人：</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="n"/>
-      <c r="G33" s="2" t="n"/>
-    </row>
-    <row r="34" ht="34" customFormat="1" customHeight="1" s="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>总监理工程师：</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="n"/>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>部门负责人：</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>审核人：</t>
-        </is>
-      </c>
-    </row>
+    <row r="18" ht="33" customHeight="1" s="14"/>
+    <row r="19" ht="25" customHeight="1" s="14"/>
+    <row r="20" ht="25" customHeight="1" s="14"/>
+    <row r="21" ht="25" customFormat="1" customHeight="1" s="1"/>
+    <row r="22" ht="25" customFormat="1" customHeight="1" s="1"/>
+    <row r="23" ht="25" customFormat="1" customHeight="1" s="1"/>
+    <row r="24" ht="25" customFormat="1" customHeight="1" s="1"/>
+    <row r="25" ht="25" customFormat="1" customHeight="1" s="1"/>
+    <row r="26" ht="25" customFormat="1" customHeight="1" s="1"/>
+    <row r="27" ht="25" customFormat="1" customHeight="1" s="1"/>
+    <row r="28" ht="25" customFormat="1" customHeight="1" s="1"/>
+    <row r="29" ht="25" customFormat="1" customHeight="1" s="1"/>
+    <row r="30" ht="25" customFormat="1" customHeight="1" s="1"/>
+    <row r="31" ht="25" customFormat="1" customHeight="1" s="1"/>
+    <row r="32" ht="34" customFormat="1" customHeight="1" s="1"/>
+    <row r="33" ht="34" customFormat="1" customHeight="1" s="1"/>
+    <row r="34" ht="34" customFormat="1" customHeight="1" s="1"/>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="10">
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="F19:G19"/>
     <mergeCell ref="B2:B3"/>
+    <mergeCell ref="D2:D3"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="E19:E20"/>
-    <mergeCell ref="D2:D3"/>
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="E2:E3"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="H19:H20"/>
-    <mergeCell ref="A18:H18"/>
     <mergeCell ref="F2:G2"/>
-    <mergeCell ref="A32:B32"/>
     <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="A31:H31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" scale="96" fitToHeight="0"/>
